--- a/src/plugin-tables/relay-plugin-tables-v0.9.xlsx
+++ b/src/plugin-tables/relay-plugin-tables-v0.9.xlsx
@@ -1640,7 +1640,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>注：对照正文 HTML 4.4 初稿档位（0.2–2.0）；新版为建议区间，待拍板后回写 HTML 4.4。</t>
+          <t>注：对照正文 HTML 4.4 初稿档位（0.2–2.0）；新版区间已回写 HTML 4.4（2026-09-29，双作用域）。</t>
         </is>
       </c>
     </row>

--- a/src/plugin-tables/relay-plugin-tables-v0.9.xlsx
+++ b/src/plugin-tables/relay-plugin-tables-v0.9.xlsx
@@ -1793,7 +1793,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>效率继承计算（乘法叠加，沿用正文 4.4）：根卡默认 100%，每经一层中继即乘该插件效率。双作用域下，命中同时放大伤害与附着条推进速度。</t>
+          <t>效率继承计算（乘法叠加，沿用正文 4.4）：根行为插件默认 100%，每经一层中继即乘该插件效率。双作用域下，命中同时放大伤害与附着条推进速度。</t>
         </is>
       </c>
     </row>

--- a/src/plugin-tables/relay-plugin-tables-v0.9.xlsx
+++ b/src/plugin-tables/relay-plugin-tables-v0.9.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,6 +124,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -494,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -596,10 +602,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>v0.9c 扩充（2026-10-01）</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>概念定稿：触发 = 中继专属职责——中继必须满足触发条件才触发，条件苛刻度门控效率；形态改变类玩法（公转等）归赋能侧「依据上游改变形态」。新增 5 个中继插件：殉爆接力（召唤物销毁触发）、蓄能齐射（上游命中累计 N 次触发）、感电回路（命中感电敌人触发）、致命引信（上游命中暴击触发）、走时回路（每 X 秒自动触发）；主表 9→24 行；Tag 体系补「命中暴击」并激活「召唤物销毁 / 累积 / 计时」的配套中继。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>基于 2026-09-25《插件体系扩展·讨论结论》修订于 2026-09-29；效率档位与载荷设计对照正文 HTML 4.4「触发条件档位表」与 4.9 状态数值体系。</t>
         </is>
@@ -727,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1146,17 +1164,124 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>殉爆接力</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>己方召唤物销毁（自然到期 / 超限替换）时触发（事件·召唤物销毁·极苛刻）</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>RL_LAST_I</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>注1：效率已按「稀有度体系 · 动态平衡公式」计算：II = 基准×1.10（2分支）或 ×1.20（1分支）；III = 基准×1.30（2分支）或 ×1.20（3分支）。</t>
         </is>
       </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>殉爆接力</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>己方召唤物销毁（自然到期 / 超限替换）时触发（事件·召唤物销毁·极苛刻）</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>RL_LAST_II</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>注2：载荷为固定档，不随稀有度变化（事件10 / 跨树15 / 控制20）。</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>殉爆接力</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>己方召唤物销毁（自然到期 / 超限替换）时触发（事件·召唤物销毁·极苛刻）</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>RL_LAST_III</t>
         </is>
       </c>
     </row>
@@ -1164,6 +1289,469 @@
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>注3：分支配置为各稀有度设计初稿——连击（简单触发）只走效率轴不加分支；灼芯（跨树）II 起一拖二、不超 2 分支；失衡（控制）III 才给三分支（极少数）。均可按稀有度单独调整。</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>蓄能齐射</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>上游技能命中累计 N 次后触发（N=8 次一充；I 档）（累积·中等）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>RL_VOLLEY_I</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>蓄能齐射</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>上游技能命中累计 N 次后触发（II=6 次、III=5 次，充能更快）</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>RL_VOLLEY_II</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>蓄能齐射</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>上游技能命中累计 N 次后触发（II=6 次、III=5 次，充能更快）</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>RL_VOLLEY_III</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>感电回路</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>命中处于「感电」状态的敌人时触发（须他树先制造感电；状态·跨树·苛刻）</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>RL_VOLT_I</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>感电回路</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>命中处于「感电」状态的敌人时触发（须他树先制造感电；状态·跨树·苛刻）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>RL_VOLT_II</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>感电回路</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>命中处于「感电」状态的敌人时触发（须他树先制造感电；状态·跨树·苛刻）</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>RL_VOLT_III</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>致命引信</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>上游技能命中且判定为暴击时触发（基础暴击率 0%，须先经精准校准等制造暴击；事件·中等）</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>RL_CRIT_I</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>致命引信</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>上游技能命中且判定为暴击时触发（基础暴击率 0%，须先经精准校准等制造暴击；事件·中等）</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>RL_CRIT_II</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>致命引信</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>上游技能命中且判定为暴击时触发（基础暴击率 0%，须先经精准校准等制造暴击；事件·中等）</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>RL_CRIT_III</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>走时回路</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>距上游技能上次释放满 X 秒（X=3s）后自动触发（计时·无门槛/极简单）</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>RL_TICK_I</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>走时回路</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>距上游技能上次释放满 X 秒（X=3s）后自动触发（计时·无门槛/极简单）</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>RL_TICK_II</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>走时回路</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>距上游技能上次释放满 X 秒（X=3s）后自动触发（计时·无门槛/极简单）</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>0.5s</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>RL_TICK_III</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1246,7 +1834,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>本中继计数的释放/命中次数达到 N 后触发</t>
+          <t>上游技能命中/释放累计 N 次后触发（v0.9c：蓄能齐射 N=8/6/5）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -1268,7 +1856,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>距本中继上次触发满 X 秒后触发</t>
+          <t>距上游技能上次释放满 X 秒后触发（v0.9c：走时回路 X=3s）</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1278,7 +1866,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>简单/中等</t>
+          <t>极简单</t>
         </is>
       </c>
     </row>
@@ -1351,43 +1939,72 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>命中暴击</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>上游技能命中且判定为暴击时触发</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>暴击基础率 0%，须先经精准校准等制造暴击</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>召唤物销毁</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>己方召唤物自然到期、或因超上限被替换而销毁时触发</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>须装配召唤类行为插件；寿命=定时引信</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>苛刻(事件型)</t>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>极苛刻(事件型)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>触发条件的跨树原则：中继触发条件只能引用「其他树制造」的状态（一棵树不得自产自销状态）——状态需由 A 树制造，B 树的中继消费。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>第 5 类「召唤物销毁」由 2026-09-26 浮游机炮落地：召唤物寿命构成定时引信，自然到期/替换统一触发销毁中继。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>「命中燃烧 / 命中感电 / 命中失衡」均不计较状态由哪棵他树制造，只要求目标当前处于该状态。</t>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>v0.9c（2026-10-01）：「命中感电」已配感电回路、「命中暴击」已配致命引信（新增 Tag）、「累积」已配蓄能齐射、「计时」已配走时回路、「召唤物销毁」已配殉爆接力——全部触发条件 Tag 均有配套中继。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>概念定稿（2026-10-01）：中继必须满足触发条件才触发；触发条件的苛刻度门控效率；「命中后触发 N 次」类简单连发不做（用户裁定）——重复触发交给「累积充能」型（蓄能齐射）表达。</t>
         </is>
       </c>
     </row>
@@ -1503,14 +2120,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>动态平衡公式（初稿可调）：效率(X) = 基准效率 × ( 1 + a_X − 0.10 × (分支数 − 1) )，其中 a_I=0.00 / a_II=0.20 / a_III=0.40。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>计算示例（失衡爆破 · 基准 1.33）：</t>
         </is>
@@ -1615,7 +2232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1631,14 +2248,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>效率作用域（v0.9 扩大）：① 被触发行为插件的伤害；② 其异常附着效率（状态值累计速度）。因双作用同时放大，档位差距拉开、易触发档下调、极苛刻档上限抬升。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>注：对照正文 HTML 4.4 初稿档位（0.2–2.0）；新版区间已回写 HTML 4.4（2026-09-29，双作用域）。</t>
         </is>
@@ -1647,151 +2264,158 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>触发条件档位</t>
+          <t>本表中继基准（I 档）锚点</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>示例</t>
+          <t>触发条件</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>效率区间（新·初稿）</t>
+          <t>效率（I）· 载荷</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>无门槛 / 极简单</t>
+          <t>连击链动</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>技能结束时触发、每 X 秒触发</t>
+          <t>击中（简单）</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.10 – 0.20</t>
+          <t>0.25 · 10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>蓄能齐射</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>击中时触发、命中 N 次触发</t>
+          <t>上游命中累计 N 次（中等）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>0.20 – 0.35</t>
+          <t>0.65 · 10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>致命引信</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>累积释放 10 次触发、暴击时触发</t>
+          <t>上游命中暴击（中等）</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>0.50 – 0.80</t>
+          <t>0.75 · 15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>苛刻</t>
+          <t>感电回路</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>命中燃烧 / 感电敌人（跨树制造）</t>
+          <t>命中感电（苛刻跨树）</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>1.00 – 1.40</t>
+          <t>0.90 · 15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>极苛刻</t>
+          <t>灼芯回路</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>命中失衡敌人（控制态）/ 召唤物销毁</t>
+          <t>命中燃烧（苛刻跨树）</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>1.80 – 2.40</t>
+          <t>0.84 · 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>走时回路</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>每 X 秒（极简单）</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0.18 · 10</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>本表三中继基准（I 档）锚点</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>连击链动（简单）</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>灼芯回路（苛刻）</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>失衡爆破（极苛刻）</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>殉爆接力</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>召唤物销毁（极苛刻·事件）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>1.50 · 20</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>效率（I），载荷</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>0.25 · 10</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>0.84 · 15</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>失衡爆破</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>命中失衡（极苛刻·控制）</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>1.33 · 20</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>效率继承计算（乘法叠加，沿用正文 4.4）：根行为插件默认 100%，每经一层中继即乘该插件效率。双作用域下，命中同时放大伤害与附着条推进速度。</t>
         </is>
